--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/createWorkoutSessionSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/createWorkoutSessionSchema-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="162">
-  <si>
-    <t>Statement: createWorkoutSessionSchema – validate input for creating a workout session.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="169">
+  <si>
+    <t>Statement: createWorkoutSessionSchema – Validates input for creating a workout session using Zod safeParse. Returns { success: true, data } when all required fields are present and satisfy their constraints. Returns { success: false, error } with a path pointing to the offending field when any constraint is violated. memberId is required (at least 1 character after trimming, not whitespace-only; surrounding whitespace trimmed). date is required and must be in YYYY-MM-DD format. duration is required and must be an integer in the range 0–180 inclusive. notes is optional; when present it accepts an empty string, a whitespace-only string trimmed to "", or a non-empty string up to 1024 characters after trimming; surrounding whitespace trimmed.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: { memberId: string, date: string, duration: number, notes?: string }</t>
+    <t>Input: CreateWorkoutSessionInput { memberId: string, date: string, duration: number, notes?: string }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>memberId non-empty | date YYYY-MM-DD | 0 ≤ duration ≤ 180 | notes 0-1024</t>
+    <t>Input is passed directly to createWorkoutSessionSchema.safeParse(). memberId: required, at least 1 character after trim, not whitespace-only. date: required, YYYY-MM-DD format. duration: required, integer, 0 ≤ duration ≤ 180. notes: optional; when present, trimmed before length check, max 1024 characters after trim, whitespace-only trimmed to "".</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: { success: true, data } OR { success: false, error }</t>
+    <t>Output: { success: boolean, data?: CreateWorkoutSessionInput, error?: ZodError }</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Validation results match constraints.</t>
+    <t>On success: parsed data contains the supplied fields with memberId and notes trimmed. On failure: error.issues[0].path contains the name of the offending field.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -67,64 +67,64 @@
     <t>All fields valid</t>
   </si>
   <si>
-    <t>All fields correct</t>
-  </si>
-  <si>
-    <t>Notes presence</t>
-  </si>
-  <si>
-    <t>Absent</t>
-  </si>
-  <si>
-    <t>Notes value</t>
-  </si>
-  <si>
-    <t>Empty string</t>
-  </si>
-  <si>
-    <t>MemberId presence</t>
-  </si>
-  <si>
-    <t>Present</t>
-  </si>
-  <si>
-    <t>Missing</t>
-  </si>
-  <si>
-    <t>Date presence</t>
-  </si>
-  <si>
-    <t>Duration presence</t>
-  </si>
-  <si>
-    <t>MemberId value</t>
-  </si>
-  <si>
-    <t>Non-whitespace</t>
-  </si>
-  <si>
-    <t>Whitespace only</t>
-  </si>
-  <si>
-    <t>Date format</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t>Invalid format</t>
-  </si>
-  <si>
-    <t>MemberId whitespace</t>
-  </si>
-  <si>
-    <t>Surrounding (trimmed)</t>
-  </si>
-  <si>
-    <t>Notes whitespace</t>
-  </si>
-  <si>
-    <t>Whitespace only (trimmed to "")</t>
+    <t>All required fields present with valid values, notes present and valid → success: true, parsed data matches trimmed input</t>
+  </si>
+  <si>
+    <t>notes presence</t>
+  </si>
+  <si>
+    <t>notes field absent → success: true, parsed notes is undefined</t>
+  </si>
+  <si>
+    <t>notes value</t>
+  </si>
+  <si>
+    <t>notes: "" (empty string) → success: true, parsed notes is ""</t>
+  </si>
+  <si>
+    <t>memberId presence</t>
+  </si>
+  <si>
+    <t>memberId field absent → success: false, error path contains "memberId"</t>
+  </si>
+  <si>
+    <t>date presence</t>
+  </si>
+  <si>
+    <t>date field absent → success: false, error path contains "date"</t>
+  </si>
+  <si>
+    <t>duration presence</t>
+  </si>
+  <si>
+    <t>duration field absent → success: false, error path contains "duration"</t>
+  </si>
+  <si>
+    <t>memberId value</t>
+  </si>
+  <si>
+    <t>memberId: "   " (whitespace-only) → success: false, error path contains "memberId"</t>
+  </si>
+  <si>
+    <t>date format</t>
+  </si>
+  <si>
+    <t>date: "2024-01-01" (valid YYYY-MM-DD) → success: true</t>
+  </si>
+  <si>
+    <t>date: "01/01/2024" (MM/DD/YYYY, wrong format) → success: false, error path contains "date"</t>
+  </si>
+  <si>
+    <t>memberId whitespace</t>
+  </si>
+  <si>
+    <t>memberId: "  member-123  " (surrounding whitespace) → success: true, parsed memberId is "member-123"</t>
+  </si>
+  <si>
+    <t>notes content</t>
+  </si>
+  <si>
+    <t>notes: "  some notes  " (surrounding whitespace) → success: true, parsed notes is "some notes"; notes: "     " (whitespace-only) → success: true, parsed notes is ""</t>
   </si>
   <si>
     <t>No TC</t>
@@ -145,10 +145,10 @@
     <t>EC-1</t>
   </si>
   <si>
-    <t>Valid session data</t>
-  </si>
-  <si>
-    <t>success: true</t>
+    <t>all required fields provided with valid values: memberId "member-123", date "2024-01-01", duration 60, notes "Session notes"</t>
+  </si>
+  <si>
+    <t>success: true, parsed data matches trimmed input</t>
   </si>
   <si>
     <t>Passed</t>
@@ -157,61 +157,79 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>Notes absent</t>
+    <t>valid session data with notes field absent</t>
+  </si>
+  <si>
+    <t>success: true, parsed notes is undefined</t>
   </si>
   <si>
     <t>EC-3</t>
   </si>
   <si>
-    <t>Notes=""</t>
+    <t>valid session data with notes: "" (empty string)</t>
+  </si>
+  <si>
+    <t>success: true, parsed notes is ""</t>
   </si>
   <si>
     <t>EC-4</t>
   </si>
   <si>
-    <t>Missing memberId</t>
-  </si>
-  <si>
-    <t>success: false</t>
+    <t>session data with memberId field absent</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "memberId"</t>
   </si>
   <si>
     <t>EC-5</t>
   </si>
   <si>
-    <t>Missing date</t>
+    <t>session data with date field absent</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "date"</t>
   </si>
   <si>
     <t>EC-6</t>
   </si>
   <si>
-    <t>Missing duration</t>
+    <t>session data with duration field absent</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "duration"</t>
   </si>
   <si>
     <t>EC-7</t>
   </si>
   <si>
-    <t>memberId="   "</t>
+    <t>valid session data with memberId: "   " (whitespace-only)</t>
   </si>
   <si>
     <t>EC-8</t>
   </si>
   <si>
-    <t>date="01/01/2024"</t>
+    <t>valid session data with date: "01/01/2024" (MM/DD/YYYY, wrong format)</t>
   </si>
   <si>
     <t>EC-9</t>
   </si>
   <si>
-    <t>memberId="  member-123  " (padded)</t>
+    <t>valid session data with memberId: "  member-123  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>success: true, parsed memberId is "member-123"</t>
   </si>
   <si>
     <t>EC-10</t>
   </si>
   <si>
-    <t>notes="     " (whitespace only)</t>
-  </si>
-  <si>
-    <t>notes="  some notes  " (padded)</t>
+    <t>valid session data with notes: "     " (whitespace-only)</t>
+  </si>
+  <si>
+    <t>valid session data with notes: "  some notes  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>success: true, parsed notes is "some notes"</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -220,160 +238,196 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>MemberId length</t>
-  </si>
-  <si>
-    <t>0 chars (Below Min)</t>
-  </si>
-  <si>
-    <t>1 char (At Min)</t>
-  </si>
-  <si>
-    <t>2 chars (Above Min)</t>
-  </si>
-  <si>
-    <t>Duration range</t>
-  </si>
-  <si>
-    <t>-1 (Below Min)</t>
-  </si>
-  <si>
-    <t>0 (At Min)</t>
-  </si>
-  <si>
-    <t>1 (Above Min)</t>
-  </si>
-  <si>
-    <t>179 (Below Max)</t>
-  </si>
-  <si>
-    <t>180 (At Max)</t>
-  </si>
-  <si>
-    <t>181 (Above Max)</t>
-  </si>
-  <si>
-    <t>Notes length</t>
-  </si>
-  <si>
-    <t>0 chars (At Min)</t>
-  </si>
-  <si>
-    <t>1 char (Above Min)</t>
-  </si>
-  <si>
-    <t>1023 chars (Below Max)</t>
-  </si>
-  <si>
-    <t>1024 chars (At Max)</t>
-  </si>
-  <si>
-    <t>1025 chars (Above Max)</t>
-  </si>
-  <si>
-    <t>1 char padded (At Min after trim)</t>
-  </si>
-  <si>
-    <t>1024 chars padded (At Max after trim)</t>
+    <t>memberId length</t>
+  </si>
+  <si>
+    <t>memberId: "" (length 0, min - 1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>memberId: "A" (length 1, min): at minimum → success: true, parsed memberId is "A"</t>
+  </si>
+  <si>
+    <t>memberId: "AB" (length 2, min + 1): above minimum → success: true, parsed memberId is "AB"</t>
+  </si>
+  <si>
+    <t>duration range</t>
+  </si>
+  <si>
+    <t>duration: -1 (min - 1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>duration: 0 (min): at minimum → success: true, parsed duration is 0</t>
+  </si>
+  <si>
+    <t>duration: 1 (min + 1): above minimum → success: true, parsed duration is 1</t>
+  </si>
+  <si>
+    <t>duration: 179 (max - 1): below maximum → success: true, parsed duration is 179</t>
+  </si>
+  <si>
+    <t>duration: 180 (max): at maximum → success: true, parsed duration is 180</t>
+  </si>
+  <si>
+    <t>duration: 181 (max + 1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>notes length</t>
+  </si>
+  <si>
+    <t>notes: "" (length 0, min): at minimum → success: true, parsed notes is ""</t>
+  </si>
+  <si>
+    <t>notes: "A" (length 1, min + 1): above minimum → success: true, parsed notes is "A"</t>
+  </si>
+  <si>
+    <t>notes: "A".repeat(1023) (max - 1): below maximum → success: true</t>
+  </si>
+  <si>
+    <t>notes: "A".repeat(1024) (max): at maximum → success: true</t>
+  </si>
+  <si>
+    <t>notes: "A".repeat(1025) (max + 1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>memberId whitespace + trim</t>
+  </si>
+  <si>
+    <t>memberId: " A " (1 real char after trim, at minimum) → success: true, parsed memberId is "A"</t>
+  </si>
+  <si>
+    <t>notes whitespace + trim</t>
+  </si>
+  <si>
+    <t>notes: " " + "A".repeat(1024) + " " (1024 real chars after trim, at maximum) → success: true, parsed notes is "A".repeat(1024)</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 MemId 0ch</t>
-  </si>
-  <si>
-    <t>memberId=""</t>
-  </si>
-  <si>
-    <t>BVA-1 MemId 1ch</t>
-  </si>
-  <si>
-    <t>memberId="A"</t>
-  </si>
-  <si>
-    <t>BVA-1 MemId 2ch</t>
-  </si>
-  <si>
-    <t>memberId="AB"</t>
-  </si>
-  <si>
-    <t>BVA-2 Dur -1</t>
-  </si>
-  <si>
-    <t>duration=-1</t>
-  </si>
-  <si>
-    <t>BVA-2 Dur 0</t>
-  </si>
-  <si>
-    <t>duration=0</t>
-  </si>
-  <si>
-    <t>BVA-2 Dur 1</t>
-  </si>
-  <si>
-    <t>duration=1</t>
-  </si>
-  <si>
-    <t>BVA-2 Dur 179</t>
-  </si>
-  <si>
-    <t>duration=179</t>
-  </si>
-  <si>
-    <t>BVA-2 Dur 180</t>
-  </si>
-  <si>
-    <t>duration=180</t>
-  </si>
-  <si>
-    <t>BVA-2 Dur 181</t>
-  </si>
-  <si>
-    <t>duration=181</t>
-  </si>
-  <si>
-    <t>BVA-3 Notes 0ch</t>
-  </si>
-  <si>
-    <t>notes len 0</t>
-  </si>
-  <si>
-    <t>BVA-3 Notes 1ch</t>
-  </si>
-  <si>
-    <t>notes len 1</t>
-  </si>
-  <si>
-    <t>BVA-3 Notes 1023ch</t>
-  </si>
-  <si>
-    <t>notes len 1023</t>
-  </si>
-  <si>
-    <t>BVA-3 Notes 1024ch</t>
-  </si>
-  <si>
-    <t>notes len 1024</t>
-  </si>
-  <si>
-    <t>BVA-3 Notes 1025ch</t>
-  </si>
-  <si>
-    <t>notes len 1025</t>
-  </si>
-  <si>
-    <t>BVA-4 MemId padded 1ch</t>
-  </si>
-  <si>
-    <t>memberId=" A "</t>
-  </si>
-  <si>
-    <t>BVA-5 Notes padded 1024ch</t>
-  </si>
-  <si>
-    <t>notes=" "+"A".repeat(1024)+" "</t>
+    <t>BVA-1  (memberId=0)</t>
+  </si>
+  <si>
+    <t>valid session data with memberId: "" (0 characters)</t>
+  </si>
+  <si>
+    <t>BVA-2  (memberId=1)</t>
+  </si>
+  <si>
+    <t>valid session data with memberId: "A" (1 character)</t>
+  </si>
+  <si>
+    <t>success: true, parsed memberId is "A"</t>
+  </si>
+  <si>
+    <t>BVA-3  (memberId=2)</t>
+  </si>
+  <si>
+    <t>valid session data with memberId: "AB" (2 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed memberId is "AB"</t>
+  </si>
+  <si>
+    <t>BVA-4  (dur=-1)</t>
+  </si>
+  <si>
+    <t>valid session data with duration: -1</t>
+  </si>
+  <si>
+    <t>BVA-5  (dur=0)</t>
+  </si>
+  <si>
+    <t>valid session data with duration: 0</t>
+  </si>
+  <si>
+    <t>success: true, parsed duration is 0</t>
+  </si>
+  <si>
+    <t>BVA-6  (dur=1)</t>
+  </si>
+  <si>
+    <t>valid session data with duration: 1</t>
+  </si>
+  <si>
+    <t>success: true, parsed duration is 1</t>
+  </si>
+  <si>
+    <t>BVA-7  (dur=179)</t>
+  </si>
+  <si>
+    <t>valid session data with duration: 179</t>
+  </si>
+  <si>
+    <t>success: true, parsed duration is 179</t>
+  </si>
+  <si>
+    <t>BVA-8  (dur=180)</t>
+  </si>
+  <si>
+    <t>valid session data with duration: 180</t>
+  </si>
+  <si>
+    <t>success: true, parsed duration is 180</t>
+  </si>
+  <si>
+    <t>BVA-9  (dur=181)</t>
+  </si>
+  <si>
+    <t>valid session data with duration: 181</t>
+  </si>
+  <si>
+    <t>BVA-10 (notes=0)</t>
+  </si>
+  <si>
+    <t>valid session data with notes: "" (0 characters)</t>
+  </si>
+  <si>
+    <t>BVA-11 (notes=1)</t>
+  </si>
+  <si>
+    <t>valid session data with notes: "A" (1 character)</t>
+  </si>
+  <si>
+    <t>success: true, parsed notes is "A"</t>
+  </si>
+  <si>
+    <t>BVA-12 (notes=1023)</t>
+  </si>
+  <si>
+    <t>valid session data with notes: "A".repeat(1023) (1023 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed notes is "A".repeat(1023)</t>
+  </si>
+  <si>
+    <t>BVA-13 (notes=1024)</t>
+  </si>
+  <si>
+    <t>valid session data with notes: "A".repeat(1024) (1024 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed notes is "A".repeat(1024)</t>
+  </si>
+  <si>
+    <t>BVA-14 (notes=1025)</t>
+  </si>
+  <si>
+    <t>valid session data with notes: "A".repeat(1025) (1025 characters)</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "notes"</t>
+  </si>
+  <si>
+    <t>BVA-15 (pad→1)</t>
+  </si>
+  <si>
+    <t>valid session data with memberId: " A " (1 real character after trim)</t>
+  </si>
+  <si>
+    <t>BVA-16 (pad→1024)</t>
+  </si>
+  <si>
+    <t>valid session data with notes: " " + "A".repeat(1024) + " " (1024 real characters after trim)</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -382,85 +436,52 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Valid session (All fields)</t>
-  </si>
-  <si>
-    <t>Notes field absent</t>
-  </si>
-  <si>
-    <t>Notes empty string</t>
-  </si>
-  <si>
-    <t>MemberId missing</t>
-  </si>
-  <si>
-    <t>Date field missing</t>
-  </si>
-  <si>
-    <t>Duration field missing</t>
-  </si>
-  <si>
-    <t>MemberId whitespace "   "</t>
-  </si>
-  <si>
-    <t>Date format wrong "01/01/2024"</t>
-  </si>
-  <si>
-    <t>MemberId with surrounding whitespace</t>
-  </si>
-  <si>
-    <t>Notes whitespace-only</t>
-  </si>
-  <si>
-    <t>Notes with surrounding whitespace</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>memberId empty ""</t>
-  </si>
-  <si>
-    <t>memberId length 1</t>
-  </si>
-  <si>
-    <t>memberId length 2</t>
-  </si>
-  <si>
     <t>BVA-2</t>
   </si>
   <si>
-    <t>duration -1 (Below Min)</t>
-  </si>
-  <si>
-    <t>duration 0 (At Min)</t>
-  </si>
-  <si>
-    <t>duration 1 (Above Min)</t>
-  </si>
-  <si>
-    <t>duration 179 (Below Max)</t>
-  </si>
-  <si>
-    <t>duration 180 (At Max)</t>
-  </si>
-  <si>
-    <t>duration 181 (Above Max)</t>
-  </si>
-  <si>
     <t>BVA-3</t>
   </si>
   <si>
     <t>BVA-4</t>
   </si>
   <si>
-    <t>memberId length 1 padded with whitespace</t>
-  </si>
-  <si>
     <t>BVA-5</t>
   </si>
   <si>
-    <t>notes length 1024 padded with whitespace</t>
+    <t>BVA-6</t>
+  </si>
+  <si>
+    <t>BVA-7</t>
+  </si>
+  <si>
+    <t>BVA-8</t>
+  </si>
+  <si>
+    <t>BVA-9</t>
+  </si>
+  <si>
+    <t>BVA-10</t>
+  </si>
+  <si>
+    <t>BVA-11</t>
+  </si>
+  <si>
+    <t>BVA-12</t>
+  </si>
+  <si>
+    <t>BVA-13</t>
+  </si>
+  <si>
+    <t>BVA-14</t>
+  </si>
+  <si>
+    <t>BVA-15</t>
+  </si>
+  <si>
+    <t>BVA-16</t>
   </si>
   <si>
     <t>Testing</t>
@@ -493,7 +514,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>WSM-01</t>
+    <t>SCHEMA-09</t>
   </si>
   <si>
     <t>n/a</t>
@@ -1090,10 +1111,10 @@
         <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1101,13 +1122,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1118,10 +1139,10 @@
         <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1129,10 +1150,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>28</v>
@@ -1174,10 +1195,10 @@
         <v>34</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1243,7 +1264,7 @@
         <v>46</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>44</v>
@@ -1254,13 +1275,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>44</v>
@@ -1271,13 +1292,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>44</v>
@@ -1288,13 +1309,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>44</v>
@@ -1305,13 +1326,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>44</v>
@@ -1322,13 +1343,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>44</v>
@@ -1339,13 +1360,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>44</v>
@@ -1356,13 +1377,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>44</v>
@@ -1373,13 +1394,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>44</v>
@@ -1390,13 +1411,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>44</v>
@@ -1420,13 +1441,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1434,175 +1455,175 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+      <c r="A3" s="1">
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
+      <c r="A4" s="1">
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
+      <c r="A6" s="1">
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
+      <c r="A7" s="1">
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>1</v>
+      <c r="A8" s="1">
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
+      <c r="A9" s="1">
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>1</v>
+      <c r="A10" s="1">
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>1</v>
+      <c r="A12" s="1">
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>1</v>
+      <c r="A13" s="1">
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>1</v>
+      <c r="A14" s="1">
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>1</v>
+      <c r="A15" s="1">
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1628,7 +1649,7 @@
         <v>36</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>38</v>
@@ -1645,13 +1666,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>44</v>
@@ -1662,13 +1683,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>44</v>
@@ -1679,13 +1700,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>44</v>
@@ -1696,13 +1717,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>44</v>
@@ -1713,13 +1734,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>44</v>
@@ -1730,13 +1751,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>44</v>
@@ -1747,13 +1768,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>44</v>
@@ -1764,13 +1785,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>44</v>
@@ -1781,13 +1802,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>44</v>
@@ -1798,13 +1819,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>44</v>
@@ -1815,13 +1836,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>44</v>
@@ -1832,13 +1853,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>44</v>
@@ -1849,13 +1870,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>44</v>
@@ -1866,13 +1887,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>51</v>
+        <v>132</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>44</v>
@@ -1883,13 +1904,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>44</v>
@@ -1900,13 +1921,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>44</v>
@@ -1936,10 +1957,10 @@
         <v>36</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>38</v>
@@ -1962,7 +1983,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>121</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>43</v>
@@ -1982,10 +2003,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>44</v>
@@ -1996,16 +2017,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>44</v>
@@ -2016,16 +2037,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>44</v>
@@ -2036,16 +2057,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>125</v>
+        <v>55</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>44</v>
@@ -2056,16 +2077,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>126</v>
+        <v>58</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>44</v>
@@ -2076,16 +2097,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>44</v>
@@ -2096,16 +2117,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>44</v>
@@ -2116,16 +2137,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>44</v>
@@ -2136,16 +2157,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>44</v>
@@ -2156,16 +2177,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>44</v>
@@ -2179,13 +2200,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>44</v>
@@ -2199,13 +2220,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>44</v>
@@ -2219,13 +2240,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>44</v>
@@ -2239,13 +2260,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>44</v>
@@ -2259,13 +2280,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>44</v>
@@ -2279,13 +2300,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>44</v>
@@ -2299,13 +2320,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>44</v>
@@ -2319,13 +2340,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>44</v>
@@ -2339,13 +2360,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>44</v>
@@ -2359,13 +2380,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>44</v>
@@ -2379,13 +2400,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>44</v>
@@ -2399,13 +2420,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>44</v>
@@ -2419,13 +2440,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>44</v>
@@ -2439,13 +2460,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>51</v>
+        <v>132</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>44</v>
@@ -2459,13 +2480,13 @@
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>44</v>
@@ -2479,13 +2500,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>44</v>
@@ -2516,16 +2537,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -2533,39 +2554,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B3" s="1">
         <v>27</v>
@@ -2580,19 +2601,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/createWorkoutSessionSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/createWorkoutSessionSchema-bbt-form.xlsx
@@ -514,7 +514,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-09</t>
+    <t>SCHEMA-11</t>
   </si>
   <si>
     <t>n/a</t>
